--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_39.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4187995.369385649</v>
+        <v>4227946.122424303</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6763872.953217701</v>
+        <v>6763872.953217629</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6763872.953217701</v>
+        <v>6763872.953217629</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3480075.510125575</v>
+        <v>3480075.510125465</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3480075.510125575</v>
+        <v>3480075.510125465</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50491776.88409032</v>
+        <v>50491776.88409036</v>
       </c>
     </row>
   </sheetData>
@@ -675,28 +675,28 @@
         <v>408.0096587035274</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>419.7382696589336</v>
+        <v>798.7814999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>98.12488247690067</v>
+        <v>66.13418277954376</v>
       </c>
       <c r="L2" t="n">
-        <v>783.0093003026282</v>
+        <v>649.5830037161325</v>
       </c>
       <c r="M2" t="n">
-        <v>512.617316149184</v>
+        <v>298.9910820919849</v>
       </c>
       <c r="N2" t="n">
         <v>195.5855355810472</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>815</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>371.9706110579117</v>
@@ -705,10 +705,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>341.419760359443</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
-        <v>586.6755817285639</v>
+        <v>283.1660146029995</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -723,7 +723,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -796,13 +796,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>317.6281094366372</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>356.5714118406279</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -900,28 +900,28 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
-        <v>102.3398200934258</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
         <v>408.0096587035274</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>97.4501913854139</v>
       </c>
       <c r="J5" t="n">
         <v>419.7382696589336</v>
       </c>
       <c r="K5" t="n">
+        <v>279.7604168367467</v>
+      </c>
+      <c r="L5" t="n">
         <v>815</v>
-      </c>
-      <c r="L5" t="n">
-        <v>279.7604168366935</v>
       </c>
       <c r="M5" t="n">
         <v>298.9910820919849</v>
@@ -930,10 +930,10 @@
         <v>195.5855355810472</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P5" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>371.9706110579117</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>547.2737972923793</v>
+        <v>317.4254924402225</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
@@ -1030,10 +1030,10 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>72.23629157494283</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1143,28 +1143,28 @@
         <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75737228701621</v>
+        <v>351.1264039897466</v>
       </c>
       <c r="H8" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>419.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>66.42124282018264</v>
+        <v>279.7604168367047</v>
       </c>
       <c r="L8" t="n">
-        <v>408.924709597565</v>
+        <v>815</v>
       </c>
       <c r="M8" t="n">
         <v>298.9910820919849</v>
       </c>
       <c r="N8" t="n">
-        <v>815</v>
+        <v>195.5855355810472</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
         <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>346.6714879340246</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1213,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>109.7879374857201</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>66.5639999646113</v>
+        <v>124.2896243480339</v>
       </c>
       <c r="T9" t="n">
         <v>405.3577652175138</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1368,22 +1368,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>224.4745782429939</v>
+        <v>167.0661201055379</v>
       </c>
       <c r="D11" t="n">
         <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
         <v>269.8481678023229</v>
@@ -1422,10 +1422,10 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>76.52251210084907</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>413.3734759809475</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>340.7767994885276</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>129.0096587035274</v>
+        <v>132.4598500889414</v>
       </c>
       <c r="I14" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>338.6387678008247</v>
+        <v>255.2652880979692</v>
       </c>
       <c r="R16" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2027,28 +2027,28 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>16.34743437468335</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>110.7176599401901</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I20" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.450191385414405</v>
       </c>
       <c r="S20" t="n">
         <v>215.8481678023229</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>255.2652880979692</v>
+        <v>377.7929984536983</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I23" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.450191385414405</v>
       </c>
       <c r="S23" t="n">
         <v>215.8481678023229</v>
@@ -2510,16 +2510,16 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>377.7929984536983</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>111.0487878059344</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
         <v>179.8896287080119</v>
@@ -2568,7 +2568,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>413.3734759809475</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>197.252545955361</v>
       </c>
     </row>
     <row r="27">
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>340.7767994885276</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>340.7767994885276</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>122.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>116.3632896068686</v>
+        <v>106.1046809922832</v>
       </c>
       <c r="F29" t="n">
         <v>116.8896287080119</v>
@@ -2814,10 +2814,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>47.83862152366675</v>
       </c>
       <c r="L29" t="n">
-        <v>47.83862152370874</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
         <v>350.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>294.0232248460821</v>
+        <v>304.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>223.3174326828064</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.5207738011430365</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>135.5476281577792</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>380.9819279128893</v>
+        <v>244.913525953967</v>
       </c>
       <c r="R31" t="n">
         <v>438.6021279811511</v>
@@ -3030,7 +3030,7 @@
         <v>161.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>112.0805471252643</v>
+        <v>122.3391557398498</v>
       </c>
       <c r="E32" t="n">
         <v>116.3632896068686</v>
@@ -3039,7 +3039,7 @@
         <v>116.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>115.7573722870162</v>
+        <v>105.4987636724307</v>
       </c>
       <c r="H32" t="n">
         <v>120.0096587035274</v>
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>47.83862152373044</v>
+        <v>47.83862152375633</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3209,31 +3209,31 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5207738011430365</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>135.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>232.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>283.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>242.0724469637387</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>245.4342997551101</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>74.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         <v>193.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>151.2159696284084</v>
+        <v>161.4745782429939</v>
       </c>
       <c r="D35" t="n">
         <v>122.3391557398498</v>
@@ -3279,7 +3279,7 @@
         <v>115.7573722870162</v>
       </c>
       <c r="H35" t="n">
-        <v>120.0096587035274</v>
+        <v>109.7510500891913</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>47.83862152373113</v>
+        <v>47.83862153205438</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>193.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>151.2159696284084</v>
+        <v>161.4745782429939</v>
       </c>
       <c r="D38" t="n">
         <v>122.3391557398498</v>
@@ -3528,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>47.83862152374645</v>
+        <v>47.83862153380133</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>361.2212965486107</v>
       </c>
       <c r="V38" t="n">
-        <v>341.8510241668239</v>
+        <v>331.5924155525415</v>
       </c>
       <c r="W38" t="n">
         <v>350.3734759809475</v>
@@ -3695,19 +3695,19 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>352.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>399.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>142.0640741896034</v>
+        <v>437.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>17.51614119014671</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3741,19 +3741,19 @@
         <v>259.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>220.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>78.07292176921794</v>
       </c>
       <c r="F41" t="n">
-        <v>214.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>213.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>218.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,10 +3783,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>60.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>304.8481678023229</v>
       </c>
       <c r="T41" t="n">
         <v>396.6755817285639</v>
@@ -3795,16 +3795,16 @@
         <v>459.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>439.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>448.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>402.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>308.9255909190275</v>
+        <v>321.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>134.4809820812256</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>224.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>91.94667871877638</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>229.8627394453875</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>38.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>9.170310216216194</v>
       </c>
       <c r="W43" t="n">
-        <v>36.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3978,7 +3978,7 @@
         <v>376.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>166.6676942987758</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -4020,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>177.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>209.5434367625695</v>
+        <v>421.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>513.6755817285639</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>556.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4054,10 +4054,10 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>288.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>268.4667575383708</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4117,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>346.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>209.7039305385027</v>
       </c>
     </row>
     <row r="46">
@@ -4297,37 +4297,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>550.8905891800684</v>
+        <v>702.4877201726792</v>
       </c>
       <c r="C2" t="n">
-        <v>500.9162677224988</v>
+        <v>652.5133987151096</v>
       </c>
       <c r="D2" t="n">
-        <v>490.4726760660849</v>
+        <v>642.0698070586957</v>
       </c>
       <c r="E2" t="n">
-        <v>486.0653128268237</v>
+        <v>637.6624438194344</v>
       </c>
       <c r="F2" t="n">
-        <v>481.126293929842</v>
+        <v>632.7234249224528</v>
       </c>
       <c r="G2" t="n">
-        <v>477.3309683874014</v>
+        <v>628.9280993800121</v>
       </c>
       <c r="H2" t="n">
-        <v>65.2</v>
+        <v>216.7971309926107</v>
       </c>
       <c r="I2" t="n">
         <v>65.2</v>
       </c>
       <c r="J2" t="n">
-        <v>448.0719498394611</v>
+        <v>65.2</v>
       </c>
       <c r="K2" t="n">
-        <v>1155.805906933501</v>
+        <v>773.5770024717948</v>
       </c>
       <c r="L2" t="n">
-        <v>1140.066629078933</v>
+        <v>924.2825542736812</v>
       </c>
       <c r="M2" t="n">
         <v>1429.121360241373</v>
@@ -4336,7 +4336,7 @@
         <v>2038.41021318981</v>
       </c>
       <c r="O2" t="n">
-        <v>2022.027889957487</v>
+        <v>2845.26021318981</v>
       </c>
       <c r="P2" t="n">
         <v>2828.877889957487</v>
@@ -4348,25 +4348,25 @@
         <v>3006.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2661.718829103295</v>
+        <v>2910.781043807457</v>
       </c>
       <c r="T2" t="n">
-        <v>2069.117231397675</v>
+        <v>2624.75476643069</v>
       </c>
       <c r="U2" t="n">
-        <v>1817.378548015241</v>
+        <v>2373.016083048255</v>
       </c>
       <c r="V2" t="n">
-        <v>1585.20579633158</v>
+        <v>2140.843331364595</v>
       </c>
       <c r="W2" t="n">
-        <v>1344.424507461936</v>
+        <v>1900.062042494951</v>
       </c>
       <c r="X2" t="n">
-        <v>1150.200433259241</v>
+        <v>1705.837968292256</v>
       </c>
       <c r="Y2" t="n">
-        <v>1037.758582064487</v>
+        <v>1189.355713057098</v>
       </c>
     </row>
     <row r="3">
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.2</v>
+        <v>416.6522089875784</v>
       </c>
       <c r="C3" t="n">
-        <v>65.2</v>
+        <v>416.6522089875784</v>
       </c>
       <c r="D3" t="n">
         <v>65.2</v>
@@ -4439,13 +4439,13 @@
         <v>809.5254966143021</v>
       </c>
       <c r="W3" t="n">
-        <v>488.6890224358807</v>
+        <v>776.82535226094</v>
       </c>
       <c r="X3" t="n">
-        <v>468.6256492587216</v>
+        <v>416.6522089875784</v>
       </c>
       <c r="Y3" t="n">
-        <v>65.2</v>
+        <v>416.6522089875784</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>489.347327138924</v>
+        <v>685.5834908579798</v>
       </c>
       <c r="C4" t="n">
-        <v>566.077758229241</v>
+        <v>811.5854966764156</v>
       </c>
       <c r="D4" t="n">
-        <v>679.3969023542411</v>
+        <v>924.9046408014157</v>
       </c>
       <c r="E4" t="n">
-        <v>797.2258065656541</v>
+        <v>1042.733545012829</v>
       </c>
       <c r="F4" t="n">
-        <v>921.5867791575896</v>
+        <v>1042.733545012829</v>
       </c>
       <c r="G4" t="n">
-        <v>1074.993345044475</v>
+        <v>1196.140110899714</v>
       </c>
       <c r="H4" t="n">
-        <v>1244.509930203872</v>
+        <v>1365.656696059112</v>
       </c>
       <c r="I4" t="n">
-        <v>1465.642809139955</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="J4" t="n">
-        <v>1465.642809139955</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="K4" t="n">
         <v>1576.007243076824</v>
@@ -4515,16 +4515,16 @@
         <v>290.525934252978</v>
       </c>
       <c r="V4" t="n">
-        <v>489.347327138924</v>
+        <v>290.525934252978</v>
       </c>
       <c r="W4" t="n">
-        <v>489.347327138924</v>
+        <v>462.4168525126554</v>
       </c>
       <c r="X4" t="n">
-        <v>489.347327138924</v>
+        <v>462.4168525126554</v>
       </c>
       <c r="Y4" t="n">
-        <v>489.347327138924</v>
+        <v>573.8261531916877</v>
       </c>
     </row>
     <row r="5">
@@ -4543,16 +4543,16 @@
         <v>992.9476168594324</v>
       </c>
       <c r="E5" t="n">
-        <v>988.5402536201711</v>
+        <v>584.4998495797671</v>
       </c>
       <c r="F5" t="n">
-        <v>885.1666979702461</v>
+        <v>579.5608306827854</v>
       </c>
       <c r="G5" t="n">
-        <v>477.3309683874014</v>
+        <v>575.7655051403448</v>
       </c>
       <c r="H5" t="n">
-        <v>65.2</v>
+        <v>163.6345367529433</v>
       </c>
       <c r="I5" t="n">
         <v>65.2</v>
@@ -4561,19 +4561,19 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K5" t="n">
-        <v>431.6896266071377</v>
+        <v>940.6648775060045</v>
       </c>
       <c r="L5" t="n">
-        <v>924.2825542736798</v>
+        <v>924.2825542736812</v>
       </c>
       <c r="M5" t="n">
-        <v>1429.121360241372</v>
+        <v>1429.121360241373</v>
       </c>
       <c r="N5" t="n">
-        <v>2038.410213189809</v>
+        <v>2038.41021318981</v>
       </c>
       <c r="O5" t="n">
-        <v>2845.260213189809</v>
+        <v>2022.027889957487</v>
       </c>
       <c r="P5" t="n">
         <v>2828.877889957487</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.2</v>
+        <v>759.7191204399794</v>
       </c>
       <c r="C6" t="n">
-        <v>65.2</v>
+        <v>759.7191204399794</v>
       </c>
       <c r="D6" t="n">
-        <v>65.2</v>
+        <v>408.2669114524009</v>
       </c>
       <c r="E6" t="n">
-        <v>65.2</v>
+        <v>408.2669114524009</v>
       </c>
       <c r="F6" t="n">
         <v>65.2</v>
@@ -4661,28 +4661,28 @@
         <v>1220.632420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>667.8306049216877</v>
+        <v>900.0006098228563</v>
       </c>
       <c r="S6" t="n">
-        <v>600.5942413210703</v>
+        <v>832.7642462222389</v>
       </c>
       <c r="T6" t="n">
-        <v>595.1823572629755</v>
+        <v>827.3523621641441</v>
       </c>
       <c r="U6" t="n">
-        <v>594.9698726567262</v>
+        <v>827.1398775578948</v>
       </c>
       <c r="V6" t="n">
-        <v>522.0039215709254</v>
+        <v>812.4826379705007</v>
       </c>
       <c r="W6" t="n">
-        <v>85.26337317715914</v>
+        <v>779.7824936171386</v>
       </c>
       <c r="X6" t="n">
-        <v>65.2</v>
+        <v>759.7191204399794</v>
       </c>
       <c r="Y6" t="n">
-        <v>65.2</v>
+        <v>759.7191204399794</v>
       </c>
     </row>
     <row r="7">
@@ -4692,25 +4692,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>638.2188222554639</v>
+        <v>1244.736612312233</v>
       </c>
       <c r="C7" t="n">
-        <v>764.2208280738997</v>
+        <v>1370.738618130669</v>
       </c>
       <c r="D7" t="n">
-        <v>877.5399721988998</v>
+        <v>1484.057762255669</v>
       </c>
       <c r="E7" t="n">
-        <v>995.3688764103129</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="F7" t="n">
-        <v>1119.729849002248</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="G7" t="n">
-        <v>1273.136414889134</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="H7" t="n">
-        <v>1442.653000048531</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="I7" t="n">
         <v>1576.007243076824</v>
@@ -4746,22 +4746,22 @@
         <v>65.2</v>
       </c>
       <c r="T7" t="n">
-        <v>65.2</v>
+        <v>253.2756791588048</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>499.8268717970915</v>
       </c>
       <c r="V7" t="n">
-        <v>264.0213928859459</v>
+        <v>698.6482646830375</v>
       </c>
       <c r="W7" t="n">
-        <v>264.0213928859459</v>
+        <v>870.5391829427149</v>
       </c>
       <c r="X7" t="n">
-        <v>415.0521839101394</v>
+        <v>1021.569973966908</v>
       </c>
       <c r="Y7" t="n">
-        <v>526.4614845891717</v>
+        <v>1132.979274645941</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>550.8905891800686</v>
+        <v>1457.405934013821</v>
       </c>
       <c r="C8" t="n">
-        <v>500.9162677224989</v>
+        <v>1407.431612556251</v>
       </c>
       <c r="D8" t="n">
-        <v>490.472676066085</v>
+        <v>1396.988020899837</v>
       </c>
       <c r="E8" t="n">
-        <v>486.0653128268237</v>
+        <v>1392.580657660576</v>
       </c>
       <c r="F8" t="n">
-        <v>77.08588988943801</v>
+        <v>983.6012347231905</v>
       </c>
       <c r="G8" t="n">
-        <v>73.29056434699739</v>
+        <v>628.9280993800121</v>
       </c>
       <c r="H8" t="n">
-        <v>65.2</v>
+        <v>216.7971309926107</v>
       </c>
       <c r="I8" t="n">
         <v>65.2</v>
@@ -4798,19 +4798,19 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K8" t="n">
-        <v>1156.443182114479</v>
+        <v>940.6648775060045</v>
       </c>
       <c r="L8" t="n">
-        <v>1550.237919894716</v>
+        <v>924.2825542736812</v>
       </c>
       <c r="M8" t="n">
-        <v>2055.076725862408</v>
+        <v>1429.121360241373</v>
       </c>
       <c r="N8" t="n">
-        <v>2038.694402630085</v>
+        <v>2038.41021318981</v>
       </c>
       <c r="O8" t="n">
-        <v>2845.544402630085</v>
+        <v>2845.26021318981</v>
       </c>
       <c r="P8" t="n">
         <v>2828.877889957487</v>
@@ -4822,25 +4822,25 @@
         <v>3260</v>
       </c>
       <c r="S8" t="n">
-        <v>2760.153365856239</v>
+        <v>3164.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>2167.551768150619</v>
+        <v>2571.592172191024</v>
       </c>
       <c r="U8" t="n">
-        <v>1817.378548015241</v>
+        <v>2319.853488808589</v>
       </c>
       <c r="V8" t="n">
-        <v>1585.20579633158</v>
+        <v>2087.680737124928</v>
       </c>
       <c r="W8" t="n">
-        <v>1344.424507461936</v>
+        <v>1846.899448255284</v>
       </c>
       <c r="X8" t="n">
-        <v>1150.200433259241</v>
+        <v>1652.67537405259</v>
       </c>
       <c r="Y8" t="n">
-        <v>1037.758582064487</v>
+        <v>1540.233522857836</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527.5491155388108</v>
+        <v>65.2</v>
       </c>
       <c r="C9" t="n">
-        <v>527.5491155388108</v>
+        <v>65.2</v>
       </c>
       <c r="D9" t="n">
-        <v>176.0969065512324</v>
+        <v>65.2</v>
       </c>
       <c r="E9" t="n">
         <v>65.2</v>
@@ -4901,25 +4901,25 @@
         <v>1071.871008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>1004.634645361474</v>
+        <v>946.3259338630676</v>
       </c>
       <c r="T9" t="n">
-        <v>595.1823572629755</v>
+        <v>536.8736457645688</v>
       </c>
       <c r="U9" t="n">
-        <v>594.9698726567262</v>
+        <v>536.6611611583195</v>
       </c>
       <c r="V9" t="n">
-        <v>580.3126330693322</v>
+        <v>522.0039215709254</v>
       </c>
       <c r="W9" t="n">
-        <v>547.61248871597</v>
+        <v>489.3037772175632</v>
       </c>
       <c r="X9" t="n">
-        <v>527.5491155388108</v>
+        <v>65.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>527.5491155388108</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="10">
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>440.0757524108052</v>
+        <v>863.5447565084419</v>
       </c>
       <c r="C10" t="n">
-        <v>566.077758229241</v>
+        <v>989.5467623268777</v>
       </c>
       <c r="D10" t="n">
-        <v>679.3969023542411</v>
+        <v>1102.865906451878</v>
       </c>
       <c r="E10" t="n">
-        <v>797.2258065656541</v>
+        <v>1102.865906451878</v>
       </c>
       <c r="F10" t="n">
-        <v>921.5867791575896</v>
+        <v>1227.226879043813</v>
       </c>
       <c r="G10" t="n">
-        <v>1074.993345044475</v>
+        <v>1380.633444930698</v>
       </c>
       <c r="H10" t="n">
-        <v>1244.509930203872</v>
+        <v>1380.633444930698</v>
       </c>
       <c r="I10" t="n">
         <v>1465.642809139955</v>
@@ -4989,16 +4989,16 @@
         <v>290.525934252978</v>
       </c>
       <c r="V10" t="n">
-        <v>290.525934252978</v>
+        <v>489.347327138924</v>
       </c>
       <c r="W10" t="n">
-        <v>290.525934252978</v>
+        <v>489.347327138924</v>
       </c>
       <c r="X10" t="n">
-        <v>290.525934252978</v>
+        <v>640.3781181631175</v>
       </c>
       <c r="Y10" t="n">
-        <v>328.3184147445131</v>
+        <v>751.7874188421498</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1207.456245745725</v>
+        <v>421.1649250963513</v>
       </c>
       <c r="C11" t="n">
-        <v>980.7142475204787</v>
+        <v>252.4112684240907</v>
       </c>
       <c r="D11" t="n">
-        <v>793.502979096388</v>
+        <v>65.2</v>
       </c>
       <c r="E11" t="n">
-        <v>612.32793908945</v>
+        <v>65.2</v>
       </c>
       <c r="F11" t="n">
-        <v>430.6212434247915</v>
+        <v>65.2</v>
       </c>
       <c r="G11" t="n">
-        <v>250.0582411146742</v>
+        <v>65.2</v>
       </c>
       <c r="H11" t="n">
         <v>65.2</v>
@@ -5032,22 +5032,22 @@
         <v>65.2</v>
       </c>
       <c r="J11" t="n">
-        <v>180.775390095766</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>890.4817564436344</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>1697.331756443634</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>2208.180585172569</v>
+        <v>967.3579417665908</v>
       </c>
       <c r="N11" t="n">
-        <v>2821.400904947332</v>
+        <v>1207.700904947333</v>
       </c>
       <c r="O11" t="n">
-        <v>2821.400904947332</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="P11" t="n">
         <v>2821.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>3260</v>
       </c>
       <c r="R11" t="n">
-        <v>3260</v>
+        <v>3233.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>2987.426093128967</v>
+        <v>2961.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>2622.097222696074</v>
+        <v>2595.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2622.097222696074</v>
+        <v>2167.450863729503</v>
       </c>
       <c r="V11" t="n">
-        <v>2544.801755927539</v>
+        <v>1758.510435278166</v>
       </c>
       <c r="W11" t="n">
-        <v>2127.252790290219</v>
+        <v>1340.961469640845</v>
       </c>
       <c r="X11" t="n">
-        <v>1756.261039319847</v>
+        <v>969.9697186704734</v>
       </c>
       <c r="Y11" t="n">
-        <v>1467.051511357417</v>
+        <v>680.7601907080427</v>
       </c>
     </row>
     <row r="12">
@@ -5111,7 +5111,7 @@
         <v>72.99487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>215.8771006891148</v>
+        <v>419.7013981428639</v>
       </c>
       <c r="K12" t="n">
         <v>627.8199167834982</v>
@@ -5208,7 +5208,7 @@
         <v>409.4189893823511</v>
       </c>
       <c r="P13" t="n">
-        <v>65.2</v>
+        <v>409.4189893823511</v>
       </c>
       <c r="Q13" t="n">
         <v>65.2</v>
@@ -5263,25 +5263,25 @@
         <v>198.9978283726681</v>
       </c>
       <c r="H14" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I14" t="n">
         <v>65.2</v>
       </c>
       <c r="J14" t="n">
-        <v>456.5091130376557</v>
+        <v>65.2</v>
       </c>
       <c r="K14" t="n">
-        <v>1166.215479385524</v>
+        <v>774.9063663478685</v>
       </c>
       <c r="L14" t="n">
-        <v>1973.065479385524</v>
+        <v>1581.756366347868</v>
       </c>
       <c r="M14" t="n">
-        <v>2483.914308114459</v>
+        <v>2092.605195076803</v>
       </c>
       <c r="N14" t="n">
-        <v>3097.134627889222</v>
+        <v>2705.825514851566</v>
       </c>
       <c r="O14" t="n">
         <v>3260</v>
@@ -5348,25 +5348,25 @@
         <v>126.454877967565</v>
       </c>
       <c r="J15" t="n">
-        <v>250.4113981428639</v>
+        <v>404.5252825072959</v>
       </c>
       <c r="K15" t="n">
-        <v>439.6042142372473</v>
+        <v>593.7180986016792</v>
       </c>
       <c r="L15" t="n">
-        <v>710.9546758324475</v>
+        <v>1141.278560196879</v>
       </c>
       <c r="M15" t="n">
-        <v>1073.245217575307</v>
+        <v>1227.359101939739</v>
       </c>
       <c r="N15" t="n">
-        <v>1465.500914107732</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O15" t="n">
-        <v>1704.543365791451</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P15" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q15" t="n">
         <v>1817.072710260958</v>
@@ -5448,10 +5448,10 @@
         <v>859.3827230120968</v>
       </c>
       <c r="Q16" t="n">
-        <v>517.3233615971224</v>
+        <v>601.5389976606127</v>
       </c>
       <c r="R16" t="n">
-        <v>65.2</v>
+        <v>149.4156360634904</v>
       </c>
       <c r="S16" t="n">
         <v>65.2</v>
@@ -5512,16 +5512,16 @@
         <v>774.9063663478685</v>
       </c>
       <c r="L17" t="n">
-        <v>890.4817564436345</v>
+        <v>1581.756366347868</v>
       </c>
       <c r="M17" t="n">
-        <v>1401.330585172569</v>
+        <v>2092.605195076803</v>
       </c>
       <c r="N17" t="n">
-        <v>2014.550904947333</v>
+        <v>2705.825514851566</v>
       </c>
       <c r="O17" t="n">
-        <v>2014.550904947333</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>2821.400904947332</v>
@@ -5582,22 +5582,22 @@
         <v>65.2</v>
       </c>
       <c r="I18" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>189.156520175299</v>
+        <v>250.4113981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>378.3493362696823</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>865.0685601968794</v>
+        <v>710.9546758324475</v>
       </c>
       <c r="M18" t="n">
-        <v>1227.359101939739</v>
+        <v>951.1491019397386</v>
       </c>
       <c r="N18" t="n">
-        <v>1360.639386547307</v>
+        <v>1084.429386547307</v>
       </c>
       <c r="O18" t="n">
         <v>1599.681838231026</v>
@@ -5670,25 +5670,25 @@
         <v>859.3827230120968</v>
       </c>
       <c r="L19" t="n">
-        <v>859.3827230120968</v>
+        <v>713.3750178022188</v>
       </c>
       <c r="M19" t="n">
-        <v>859.3827230120968</v>
+        <v>713.3750178022188</v>
       </c>
       <c r="N19" t="n">
-        <v>842.8701630376692</v>
+        <v>713.3750178022188</v>
       </c>
       <c r="O19" t="n">
-        <v>477.7736336649268</v>
+        <v>713.3750178022188</v>
       </c>
       <c r="P19" t="n">
-        <v>65.2</v>
+        <v>713.3750178022188</v>
       </c>
       <c r="Q19" t="n">
-        <v>65.2</v>
+        <v>601.5389976606127</v>
       </c>
       <c r="R19" t="n">
-        <v>65.2</v>
+        <v>149.4156360634904</v>
       </c>
       <c r="S19" t="n">
         <v>65.2</v>
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>883.6685602764463</v>
+        <v>880.1835184729979</v>
       </c>
       <c r="C20" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D20" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E20" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F20" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G20" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H20" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I20" t="n">
         <v>65.2</v>
@@ -5749,46 +5749,46 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>1166.215479385524</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="M20" t="n">
-        <v>1677.064308114459</v>
+        <v>2483.914308114459</v>
       </c>
       <c r="N20" t="n">
-        <v>2290.284627889223</v>
+        <v>3097.134627889222</v>
       </c>
       <c r="O20" t="n">
-        <v>2821.400904947332</v>
+        <v>3097.134627889222</v>
       </c>
       <c r="P20" t="n">
-        <v>2821.400904947332</v>
+        <v>3097.134627889222</v>
       </c>
       <c r="Q20" t="n">
         <v>3260</v>
       </c>
       <c r="R20" t="n">
-        <v>3260</v>
+        <v>3256.514958196551</v>
       </c>
       <c r="S20" t="n">
-        <v>3041.971547674421</v>
+        <v>3038.486505870972</v>
       </c>
       <c r="T20" t="n">
-        <v>2731.188131786983</v>
+        <v>2727.703089983534</v>
       </c>
       <c r="U20" t="n">
-        <v>2357.227226182325</v>
+        <v>2353.742184378877</v>
       </c>
       <c r="V20" t="n">
-        <v>2002.832252276443</v>
+        <v>1999.347210472994</v>
       </c>
       <c r="W20" t="n">
-        <v>1639.828741184576</v>
+        <v>1636.343699381128</v>
       </c>
       <c r="X20" t="n">
-        <v>1323.382444759659</v>
+        <v>1319.897402956211</v>
       </c>
       <c r="Y20" t="n">
-        <v>1088.718371342683</v>
+        <v>1085.233329539235</v>
       </c>
     </row>
     <row r="21">
@@ -5819,28 +5819,28 @@
         <v>65.2</v>
       </c>
       <c r="I21" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>189.156520175299</v>
+        <v>250.4113981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>378.3493362696823</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>649.6997978648824</v>
+        <v>987.1646758324475</v>
       </c>
       <c r="M21" t="n">
-        <v>1011.990339607742</v>
+        <v>1227.359101939739</v>
       </c>
       <c r="N21" t="n">
-        <v>1421.48062421531</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1660.523075899029</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P21" t="n">
-        <v>1773.052420368535</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q21" t="n">
         <v>1817.072710260958</v>
@@ -5919,13 +5919,13 @@
         <v>859.3827230120968</v>
       </c>
       <c r="P22" t="n">
-        <v>859.3827230120968</v>
+        <v>446.80908934717</v>
       </c>
       <c r="Q22" t="n">
-        <v>601.5389976606127</v>
+        <v>65.2</v>
       </c>
       <c r="R22" t="n">
-        <v>149.4156360634904</v>
+        <v>65.2</v>
       </c>
       <c r="S22" t="n">
         <v>65.2</v>
@@ -5956,46 +5956,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>883.6685602764463</v>
+        <v>880.1835184729979</v>
       </c>
       <c r="C23" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D23" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E23" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F23" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G23" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H23" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I23" t="n">
         <v>65.2</v>
       </c>
       <c r="J23" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>774.9063663478685</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1581.756366347868</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>2092.605195076803</v>
+        <v>1401.330585172569</v>
       </c>
       <c r="N23" t="n">
-        <v>2705.825514851566</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="O23" t="n">
-        <v>2821.400904947332</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="P23" t="n">
         <v>2821.400904947332</v>
@@ -6004,28 +6004,28 @@
         <v>3260</v>
       </c>
       <c r="R23" t="n">
-        <v>3260</v>
+        <v>3256.514958196551</v>
       </c>
       <c r="S23" t="n">
-        <v>3041.971547674421</v>
+        <v>3038.486505870972</v>
       </c>
       <c r="T23" t="n">
-        <v>2731.188131786983</v>
+        <v>2727.703089983534</v>
       </c>
       <c r="U23" t="n">
-        <v>2357.227226182325</v>
+        <v>2353.742184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>2002.832252276443</v>
+        <v>1999.347210472994</v>
       </c>
       <c r="W23" t="n">
-        <v>1639.828741184576</v>
+        <v>1636.343699381128</v>
       </c>
       <c r="X23" t="n">
-        <v>1323.382444759659</v>
+        <v>1319.897402956211</v>
       </c>
       <c r="Y23" t="n">
-        <v>1088.718371342683</v>
+        <v>1085.233329539235</v>
       </c>
     </row>
     <row r="24">
@@ -6056,28 +6056,28 @@
         <v>65.2</v>
       </c>
       <c r="I24" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>465.3665201752989</v>
+        <v>526.6213981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>654.5593362696823</v>
+        <v>869.9280986016793</v>
       </c>
       <c r="L24" t="n">
-        <v>925.9097978648824</v>
+        <v>1141.278560196879</v>
       </c>
       <c r="M24" t="n">
-        <v>1011.990339607742</v>
+        <v>1227.359101939739</v>
       </c>
       <c r="N24" t="n">
-        <v>1421.48062421531</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O24" t="n">
-        <v>1660.523075899029</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P24" t="n">
-        <v>1773.052420368535</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q24" t="n">
         <v>1817.072710260958</v>
@@ -6153,13 +6153,13 @@
         <v>859.3827230120968</v>
       </c>
       <c r="O25" t="n">
-        <v>859.3827230120968</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="P25" t="n">
-        <v>446.80908934717</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.2</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="R25" t="n">
         <v>65.2</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>536.760190708043</v>
+        <v>1204.576245745725</v>
       </c>
       <c r="C26" t="n">
-        <v>536.760190708043</v>
+        <v>977.8342475204787</v>
       </c>
       <c r="D26" t="n">
-        <v>536.760190708043</v>
+        <v>790.622979096388</v>
       </c>
       <c r="E26" t="n">
-        <v>424.5896979747758</v>
+        <v>609.44793908945</v>
       </c>
       <c r="F26" t="n">
-        <v>242.8830023101174</v>
+        <v>427.7412434247915</v>
       </c>
       <c r="G26" t="n">
-        <v>62.32</v>
+        <v>247.1782411146742</v>
       </c>
       <c r="H26" t="n">
         <v>62.32</v>
@@ -6220,22 +6220,22 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>1163.335479385524</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>1553.331756443634</v>
+        <v>1220.720851496278</v>
       </c>
       <c r="M26" t="n">
-        <v>2064.180585172569</v>
+        <v>1731.569680225213</v>
       </c>
       <c r="N26" t="n">
-        <v>2677.400904947332</v>
+        <v>2344.789999999976</v>
       </c>
       <c r="O26" t="n">
-        <v>2677.400904947332</v>
+        <v>2344.789999999976</v>
       </c>
       <c r="P26" t="n">
-        <v>2677.400904947332</v>
+        <v>3116</v>
       </c>
       <c r="Q26" t="n">
         <v>3116</v>
@@ -6250,19 +6250,19 @@
         <v>2451.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2023.450863729503</v>
+        <v>2451.957223879615</v>
       </c>
       <c r="V26" t="n">
-        <v>1614.510435278166</v>
+        <v>2451.957223879615</v>
       </c>
       <c r="W26" t="n">
-        <v>1196.961469640845</v>
+        <v>2034.408258242294</v>
       </c>
       <c r="X26" t="n">
-        <v>825.9697186704736</v>
+        <v>1663.416507271923</v>
       </c>
       <c r="Y26" t="n">
-        <v>536.760190708043</v>
+        <v>1464.171511357417</v>
       </c>
     </row>
     <row r="27">
@@ -6308,10 +6308,10 @@
         <v>1631.695217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.901204729126</v>
+        <v>1987.725502182875</v>
       </c>
       <c r="O27" t="n">
-        <v>2245.693656412845</v>
+        <v>2449.517953866594</v>
       </c>
       <c r="P27" t="n">
         <v>2580.973000882351</v>
@@ -6387,16 +6387,16 @@
         <v>406.5389893823511</v>
       </c>
       <c r="N28" t="n">
-        <v>406.5389893823511</v>
+        <v>62.32</v>
       </c>
       <c r="O28" t="n">
-        <v>406.5389893823511</v>
+        <v>62.32</v>
       </c>
       <c r="P28" t="n">
-        <v>406.5389893823511</v>
+        <v>62.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>406.5389893823511</v>
+        <v>62.32</v>
       </c>
       <c r="R28" t="n">
         <v>62.32</v>
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>822.7580639275434</v>
+        <v>812.3958330037195</v>
       </c>
       <c r="C29" t="n">
-        <v>659.6524293386606</v>
+        <v>649.2901984148368</v>
       </c>
       <c r="D29" t="n">
-        <v>536.0775245509335</v>
+        <v>525.7152936271098</v>
       </c>
       <c r="E29" t="n">
         <v>418.5388481803591</v>
@@ -6457,16 +6457,16 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>1163.335479385524</v>
+        <v>1162.373874771059</v>
       </c>
       <c r="L29" t="n">
-        <v>1553.331756443634</v>
+        <v>1162.373874771059</v>
       </c>
       <c r="M29" t="n">
-        <v>2064.180585172569</v>
+        <v>1673.222703499994</v>
       </c>
       <c r="N29" t="n">
-        <v>2677.400904947332</v>
+        <v>2286.443023274757</v>
       </c>
       <c r="O29" t="n">
         <v>2677.400904947332</v>
@@ -6496,10 +6496,10 @@
         <v>1541.283286639122</v>
       </c>
       <c r="X29" t="n">
-        <v>1244.290130228938</v>
+        <v>1233.927899305114</v>
       </c>
       <c r="Y29" t="n">
-        <v>1018.716965902871</v>
+        <v>1008.354734979047</v>
       </c>
     </row>
     <row r="30">
@@ -6530,25 +6530,25 @@
         <v>62.32</v>
       </c>
       <c r="I30" t="n">
-        <v>132.484877967565</v>
+        <v>123.5051259683604</v>
       </c>
       <c r="J30" t="n">
-        <v>256.4413981428639</v>
+        <v>247.4616461436594</v>
       </c>
       <c r="K30" t="n">
-        <v>721.7744622380428</v>
+        <v>436.6544622380428</v>
       </c>
       <c r="L30" t="n">
-        <v>993.1249238332429</v>
+        <v>708.0049238332429</v>
       </c>
       <c r="M30" t="n">
-        <v>1079.205465576102</v>
+        <v>794.0854655761021</v>
       </c>
       <c r="N30" t="n">
-        <v>1212.48575018367</v>
+        <v>927.3657501836705</v>
       </c>
       <c r="O30" t="n">
-        <v>1451.528201867389</v>
+        <v>1166.408201867389</v>
       </c>
       <c r="P30" t="n">
         <v>1564.057546336896</v>
@@ -6615,22 +6615,22 @@
         <v>965.3074096938342</v>
       </c>
       <c r="K31" t="n">
-        <v>965.3074096938342</v>
+        <v>964.7813755512655</v>
       </c>
       <c r="L31" t="n">
-        <v>965.3074096938342</v>
+        <v>827.8645794322965</v>
       </c>
       <c r="M31" t="n">
-        <v>965.3074096938342</v>
+        <v>827.8645794322965</v>
       </c>
       <c r="N31" t="n">
-        <v>965.3074096938342</v>
+        <v>827.8645794322965</v>
       </c>
       <c r="O31" t="n">
-        <v>965.3074096938342</v>
+        <v>827.8645794322965</v>
       </c>
       <c r="P31" t="n">
-        <v>965.3074096938342</v>
+        <v>827.8645794322965</v>
       </c>
       <c r="Q31" t="n">
         <v>580.4771794787945</v>
@@ -6673,13 +6673,13 @@
         <v>649.2901984148368</v>
       </c>
       <c r="D32" t="n">
-        <v>536.0775245509335</v>
+        <v>525.7152936271098</v>
       </c>
       <c r="E32" t="n">
-        <v>418.5388481803591</v>
+        <v>408.1766172565353</v>
       </c>
       <c r="F32" t="n">
-        <v>300.4685161520642</v>
+        <v>290.1062852282405</v>
       </c>
       <c r="G32" t="n">
         <v>183.5418774783105</v>
@@ -6691,22 +6691,22 @@
         <v>62.32</v>
       </c>
       <c r="J32" t="n">
-        <v>73.37699471019144</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>782.121756443593</v>
+        <v>1162.373874771057</v>
       </c>
       <c r="L32" t="n">
-        <v>782.121756443593</v>
+        <v>1162.373874771057</v>
       </c>
       <c r="M32" t="n">
-        <v>1292.970585172528</v>
+        <v>1673.222703499992</v>
       </c>
       <c r="N32" t="n">
+        <v>1673.222703499992</v>
+      </c>
+      <c r="O32" t="n">
         <v>1906.190904947291</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2677.400904947332</v>
       </c>
       <c r="P32" t="n">
         <v>2677.400904947332</v>
@@ -6767,25 +6767,25 @@
         <v>62.32</v>
       </c>
       <c r="I33" t="n">
-        <v>123.5051259683603</v>
+        <v>62.32</v>
       </c>
       <c r="J33" t="n">
-        <v>247.4616461436593</v>
+        <v>186.2765201752989</v>
       </c>
       <c r="K33" t="n">
-        <v>436.6544622380427</v>
+        <v>375.4693362696823</v>
       </c>
       <c r="L33" t="n">
-        <v>993.1249238332429</v>
+        <v>708.0049238332429</v>
       </c>
       <c r="M33" t="n">
-        <v>1079.205465576102</v>
+        <v>794.0854655761021</v>
       </c>
       <c r="N33" t="n">
-        <v>1212.48575018367</v>
+        <v>927.3657501836705</v>
       </c>
       <c r="O33" t="n">
-        <v>1451.528201867389</v>
+        <v>1166.408201867389</v>
       </c>
       <c r="P33" t="n">
         <v>1564.057546336896</v>
@@ -6852,28 +6852,28 @@
         <v>965.3074096938342</v>
       </c>
       <c r="K34" t="n">
-        <v>964.7813755512655</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="L34" t="n">
-        <v>827.8645794322965</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="M34" t="n">
-        <v>592.8831537731552</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="N34" t="n">
-        <v>306.8376231956956</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="O34" t="n">
-        <v>62.32</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="P34" t="n">
-        <v>62.32</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="Q34" t="n">
-        <v>62.32</v>
+        <v>580.4771794787945</v>
       </c>
       <c r="R34" t="n">
-        <v>62.32</v>
+        <v>137.4447269725813</v>
       </c>
       <c r="S34" t="n">
         <v>62.32</v>
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.3958330037195</v>
+        <v>812.3958330039715</v>
       </c>
       <c r="C35" t="n">
-        <v>659.6524293386606</v>
+        <v>649.2901984150888</v>
       </c>
       <c r="D35" t="n">
-        <v>536.0775245509335</v>
+        <v>525.7152936273617</v>
       </c>
       <c r="E35" t="n">
-        <v>418.5388481803591</v>
+        <v>408.1766172567873</v>
       </c>
       <c r="F35" t="n">
-        <v>300.4685161520642</v>
+        <v>290.1062852284924</v>
       </c>
       <c r="G35" t="n">
-        <v>183.5418774783105</v>
+        <v>173.1796465547387</v>
       </c>
       <c r="H35" t="n">
         <v>62.32</v>
@@ -6931,19 +6931,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>452.6675084231888</v>
+        <v>452.6675084230214</v>
       </c>
       <c r="L35" t="n">
-        <v>452.6675084231888</v>
+        <v>452.6675084230214</v>
       </c>
       <c r="M35" t="n">
-        <v>963.5163371521238</v>
+        <v>963.5163371519565</v>
       </c>
       <c r="N35" t="n">
-        <v>1576.736656926887</v>
+        <v>1576.73665692672</v>
       </c>
       <c r="O35" t="n">
-        <v>1906.190904947272</v>
+        <v>2347.94665692678</v>
       </c>
       <c r="P35" t="n">
         <v>2677.400904947332</v>
@@ -6952,28 +6952,28 @@
         <v>3116</v>
       </c>
       <c r="R35" t="n">
-        <v>3116</v>
+        <v>3116.000000000251</v>
       </c>
       <c r="S35" t="n">
-        <v>2907.06245676533</v>
+        <v>2907.062456765582</v>
       </c>
       <c r="T35" t="n">
-        <v>2605.369949968801</v>
+        <v>2605.369949969053</v>
       </c>
       <c r="U35" t="n">
-        <v>2240.499953455053</v>
+        <v>2240.499953455305</v>
       </c>
       <c r="V35" t="n">
-        <v>1895.195888640079</v>
+        <v>1895.195888640331</v>
       </c>
       <c r="W35" t="n">
-        <v>1541.283286639122</v>
+        <v>1541.283286639374</v>
       </c>
       <c r="X35" t="n">
-        <v>1233.927899305114</v>
+        <v>1233.927899305366</v>
       </c>
       <c r="Y35" t="n">
-        <v>1008.354734979047</v>
+        <v>1008.354734979299</v>
       </c>
     </row>
     <row r="36">
@@ -7004,22 +7004,22 @@
         <v>62.32</v>
       </c>
       <c r="I36" t="n">
-        <v>123.5051259683604</v>
+        <v>132.484877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>247.4616461436594</v>
+        <v>256.4413981428639</v>
       </c>
       <c r="K36" t="n">
-        <v>436.6544622380428</v>
+        <v>445.6342142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>708.0049238332429</v>
+        <v>716.9846758324475</v>
       </c>
       <c r="M36" t="n">
-        <v>1079.205465576102</v>
+        <v>803.0652175753067</v>
       </c>
       <c r="N36" t="n">
-        <v>1212.48575018367</v>
+        <v>936.3455021828751</v>
       </c>
       <c r="O36" t="n">
         <v>1451.528201867389</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.3958330037195</v>
+        <v>822.7580639275434</v>
       </c>
       <c r="C38" t="n">
         <v>659.6524293386606</v>
@@ -7171,13 +7171,13 @@
         <v>772.0263663478684</v>
       </c>
       <c r="L38" t="n">
-        <v>782.1217564435602</v>
+        <v>1494.914526414736</v>
       </c>
       <c r="M38" t="n">
-        <v>1292.970585172495</v>
+        <v>2005.763355143671</v>
       </c>
       <c r="N38" t="n">
-        <v>1906.190904947258</v>
+        <v>2618.983674918434</v>
       </c>
       <c r="O38" t="n">
         <v>2677.400904947332</v>
@@ -7189,28 +7189,28 @@
         <v>3116</v>
       </c>
       <c r="R38" t="n">
-        <v>3116</v>
+        <v>3116.000000000306</v>
       </c>
       <c r="S38" t="n">
-        <v>2907.06245676533</v>
+        <v>2907.062456765636</v>
       </c>
       <c r="T38" t="n">
-        <v>2605.369949968801</v>
+        <v>2605.369949969107</v>
       </c>
       <c r="U38" t="n">
-        <v>2240.499953455053</v>
+        <v>2240.499953455359</v>
       </c>
       <c r="V38" t="n">
-        <v>1895.195888640079</v>
+        <v>1905.558119563903</v>
       </c>
       <c r="W38" t="n">
-        <v>1541.283286639122</v>
+        <v>1551.645517562946</v>
       </c>
       <c r="X38" t="n">
-        <v>1233.927899305114</v>
+        <v>1244.290130228938</v>
       </c>
       <c r="Y38" t="n">
-        <v>1008.354734979047</v>
+        <v>1018.716965902871</v>
       </c>
     </row>
     <row r="39">
@@ -7241,13 +7241,13 @@
         <v>62.32</v>
       </c>
       <c r="I39" t="n">
-        <v>132.484877967565</v>
+        <v>123.5051259683603</v>
       </c>
       <c r="J39" t="n">
-        <v>256.4413981428639</v>
+        <v>247.4616461436593</v>
       </c>
       <c r="K39" t="n">
-        <v>721.7744622380428</v>
+        <v>436.6544622380427</v>
       </c>
       <c r="L39" t="n">
         <v>993.1249238332429</v>
@@ -7338,16 +7338,16 @@
         <v>965.3074096938342</v>
       </c>
       <c r="O40" t="n">
-        <v>609.3017894120009</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="P40" t="n">
-        <v>205.8190648379832</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="Q40" t="n">
-        <v>62.32</v>
+        <v>523.0455244154523</v>
       </c>
       <c r="R40" t="n">
-        <v>62.32</v>
+        <v>80.0130719092391</v>
       </c>
       <c r="S40" t="n">
         <v>62.32</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1200.168882506464</v>
+        <v>403.2770707194059</v>
       </c>
       <c r="C41" t="n">
-        <v>938.0733489276821</v>
+        <v>141.1815371406242</v>
       </c>
       <c r="D41" t="n">
-        <v>715.5085451500561</v>
+        <v>141.1815371406242</v>
       </c>
       <c r="E41" t="n">
-        <v>715.5085451500561</v>
+        <v>62.32</v>
       </c>
       <c r="F41" t="n">
-        <v>498.4483141318623</v>
+        <v>62.32</v>
       </c>
       <c r="G41" t="n">
-        <v>282.5317764682095</v>
+        <v>62.32</v>
       </c>
       <c r="H41" t="n">
         <v>62.32</v>
@@ -7402,52 +7402,52 @@
         <v>62.32</v>
       </c>
       <c r="J41" t="n">
-        <v>453.6291130376557</v>
+        <v>72.41539009576594</v>
       </c>
       <c r="K41" t="n">
-        <v>1163.335479385524</v>
+        <v>782.1217564436344</v>
       </c>
       <c r="L41" t="n">
-        <v>1163.335479385524</v>
+        <v>1553.331756443634</v>
       </c>
       <c r="M41" t="n">
-        <v>1674.184308114459</v>
+        <v>2064.180585172569</v>
       </c>
       <c r="N41" t="n">
-        <v>2287.404627889222</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>2344.78999999989</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>3116</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>3116</v>
       </c>
       <c r="R41" t="n">
-        <v>3116</v>
+        <v>3054.506465830006</v>
       </c>
       <c r="S41" t="n">
-        <v>3116</v>
+        <v>2746.579023605437</v>
       </c>
       <c r="T41" t="n">
-        <v>2715.317594213572</v>
+        <v>2345.896617819009</v>
       </c>
       <c r="U41" t="n">
-        <v>2251.457698709924</v>
+        <v>1882.036722315362</v>
       </c>
       <c r="V41" t="n">
-        <v>1807.163734905052</v>
+        <v>1882.036722315362</v>
       </c>
       <c r="W41" t="n">
-        <v>1807.163734905052</v>
+        <v>1429.134221324505</v>
       </c>
       <c r="X41" t="n">
-        <v>1807.163734905052</v>
+        <v>1022.788935000599</v>
       </c>
       <c r="Y41" t="n">
-        <v>1495.117683471691</v>
+        <v>698.2258716846327</v>
       </c>
     </row>
     <row r="42">
@@ -7487,37 +7487,37 @@
         <v>751.6693362696824</v>
       </c>
       <c r="L42" t="n">
-        <v>1057.807675796179</v>
+        <v>1211.119797864882</v>
       </c>
       <c r="M42" t="n">
-        <v>1331.988217539038</v>
+        <v>1374.952160329391</v>
       </c>
       <c r="N42" t="n">
-        <v>1653.368502146606</v>
+        <v>1696.332444936959</v>
       </c>
       <c r="O42" t="n">
-        <v>2080.510953830325</v>
+        <v>2123.474896620678</v>
       </c>
       <c r="P42" t="n">
-        <v>2381.140298299832</v>
+        <v>2424.104241090185</v>
       </c>
       <c r="Q42" t="n">
-        <v>2397.891825860257</v>
+        <v>2440.85576865061</v>
       </c>
       <c r="R42" t="n">
-        <v>2397.891825860257</v>
+        <v>2305.016392810988</v>
       </c>
       <c r="S42" t="n">
-        <v>2397.891825860257</v>
+        <v>2305.016392810988</v>
       </c>
       <c r="T42" t="n">
-        <v>2180.35872968095</v>
+        <v>2087.483296631681</v>
       </c>
       <c r="U42" t="n">
-        <v>1968.025032953488</v>
+        <v>1875.149599904219</v>
       </c>
       <c r="V42" t="n">
-        <v>1741.246581244882</v>
+        <v>1648.371148195613</v>
       </c>
       <c r="W42" t="n">
         <v>1648.371148195613</v>
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>101.4827536379986</v>
+        <v>69.31395591872287</v>
       </c>
       <c r="C43" t="n">
-        <v>101.4827536379986</v>
+        <v>69.31395591872287</v>
       </c>
       <c r="D43" t="n">
-        <v>101.4827536379986</v>
+        <v>69.31395591872287</v>
       </c>
       <c r="E43" t="n">
-        <v>101.4827536379986</v>
+        <v>69.31395591872287</v>
       </c>
       <c r="F43" t="n">
-        <v>101.4827536379986</v>
+        <v>69.31395591872287</v>
       </c>
       <c r="G43" t="n">
-        <v>101.4827536379986</v>
+        <v>69.31395591872287</v>
       </c>
       <c r="H43" t="n">
+        <v>69.31395591872287</v>
+      </c>
+      <c r="I43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="J43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="K43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="L43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="M43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="N43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="O43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="P43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="R43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="S43" t="n">
+        <v>82.54683485480578</v>
+      </c>
+      <c r="T43" t="n">
         <v>62.32</v>
       </c>
-      <c r="I43" t="n">
-        <v>75.55287893608291</v>
-      </c>
-      <c r="J43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="K43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="L43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="M43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="N43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="O43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="P43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="R43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="S43" t="n">
-        <v>129.0615474251499</v>
-      </c>
-      <c r="T43" t="n">
-        <v>108.8347125703442</v>
-      </c>
       <c r="U43" t="n">
-        <v>147.4859052086308</v>
+        <v>78.57689553106246</v>
       </c>
       <c r="V43" t="n">
-        <v>138.2229655962912</v>
+        <v>69.31395591872287</v>
       </c>
       <c r="W43" t="n">
-        <v>101.4827536379986</v>
+        <v>69.31395591872287</v>
       </c>
       <c r="X43" t="n">
-        <v>101.4827536379986</v>
+        <v>69.31395591872287</v>
       </c>
       <c r="Y43" t="n">
-        <v>101.4827536379986</v>
+        <v>69.31395591872287</v>
       </c>
     </row>
     <row r="44">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>442.5973517605999</v>
+        <v>610.9485581229998</v>
       </c>
       <c r="C44" t="n">
-        <v>62.32</v>
+        <v>230.6712063623999</v>
       </c>
       <c r="D44" t="n">
         <v>62.32</v>
@@ -7639,22 +7639,22 @@
         <v>62.32</v>
       </c>
       <c r="J44" t="n">
-        <v>62.32</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>62.32</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>833.53</v>
+        <v>521.7605851722573</v>
       </c>
       <c r="M44" t="n">
-        <v>1344.378828728935</v>
+        <v>521.7605851722573</v>
       </c>
       <c r="N44" t="n">
-        <v>1957.599148503698</v>
+        <v>1134.98090494702</v>
       </c>
       <c r="O44" t="n">
-        <v>2677.400904947332</v>
+        <v>1906.190904947176</v>
       </c>
       <c r="P44" t="n">
         <v>2677.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3116</v>
       </c>
       <c r="R44" t="n">
-        <v>3116</v>
+        <v>2936.324647648187</v>
       </c>
       <c r="S44" t="n">
-        <v>2904.339962866091</v>
+        <v>2510.2153872418</v>
       </c>
       <c r="T44" t="n">
-        <v>2385.475738897845</v>
+        <v>1991.351163273554</v>
       </c>
       <c r="U44" t="n">
-        <v>2385.475738897845</v>
+        <v>1991.351163273554</v>
       </c>
       <c r="V44" t="n">
-        <v>1822.999956911154</v>
+        <v>1991.351163273554</v>
       </c>
       <c r="W44" t="n">
-        <v>1822.999956911154</v>
+        <v>1991.351163273554</v>
       </c>
       <c r="X44" t="n">
-        <v>1298.472852405429</v>
+        <v>1466.824058767829</v>
       </c>
       <c r="Y44" t="n">
-        <v>855.7279709076449</v>
+        <v>1024.079177270045</v>
       </c>
     </row>
     <row r="45">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>624.508555539283</v>
+        <v>62.32</v>
       </c>
       <c r="C45" t="n">
-        <v>333.4985429680513</v>
+        <v>62.32</v>
       </c>
       <c r="D45" t="n">
         <v>62.32</v>
@@ -7718,22 +7718,22 @@
         <v>62.32</v>
       </c>
       <c r="J45" t="n">
-        <v>258.546520175299</v>
+        <v>186.2765201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>520.0093362696823</v>
+        <v>447.7393362696823</v>
       </c>
       <c r="L45" t="n">
-        <v>863.6297978648824</v>
+        <v>775.6866321964587</v>
       </c>
       <c r="M45" t="n">
-        <v>1021.980339607742</v>
+        <v>934.037173939318</v>
       </c>
       <c r="N45" t="n">
-        <v>1227.53062421531</v>
+        <v>1139.587458546886</v>
       </c>
       <c r="O45" t="n">
-        <v>1523.169910230605</v>
+        <v>1450.899910230605</v>
       </c>
       <c r="P45" t="n">
         <v>1635.699254700112</v>
@@ -7751,19 +7751,19 @@
         <v>1299.984340338987</v>
       </c>
       <c r="U45" t="n">
-        <v>969.4688254297073</v>
+        <v>969.4688254297075</v>
       </c>
       <c r="V45" t="n">
-        <v>624.508555539283</v>
+        <v>624.5085555392832</v>
       </c>
       <c r="W45" t="n">
-        <v>624.508555539283</v>
+        <v>624.5085555392832</v>
       </c>
       <c r="X45" t="n">
-        <v>624.508555539283</v>
+        <v>274.1421520590937</v>
       </c>
       <c r="Y45" t="n">
-        <v>624.508555539283</v>
+        <v>62.32</v>
       </c>
     </row>
     <row r="46">
@@ -7964,25 +7964,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>51.26150624509023</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>165.4169962838675</v>
       </c>
       <c r="M2" t="n">
-        <v>846.6448114931334</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8204,10 +8204,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>503.2488834659007</v>
       </c>
       <c r="L5" t="n">
-        <v>503.2488834658983</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
@@ -8216,10 +8216,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2870600406826043</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8441,22 +8441,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>716.8751175230994</v>
+        <v>503.2488834658999</v>
       </c>
       <c r="L8" t="n">
-        <v>406.0752904024351</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
         <v>885.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8675,25 +8675,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>151.7858245236418</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>720.0196279493725</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>815</v>
+        <v>814.9999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,7 +8927,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>234.7583464536658</v>
+        <v>630.0200767947325</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9155,7 +9155,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>116.7428182785516</v>
+        <v>814.9999999999999</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,10 +9164,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>186.9906878526441</v>
       </c>
       <c r="P17" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9392,7 +9392,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,13 +9401,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>606.7289575115773</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>337.3331612070587</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>814.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>781.7521334878174</v>
       </c>
       <c r="N23" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>186.9906878526441</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9863,10 +9863,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>393.9356333920305</v>
+        <v>774.8401398571939</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9878,10 +9878,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600407058</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10103,7 +10103,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>394.9069511844208</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,7 +10112,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>465.1548207585124</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>46.21168777053623</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>716.8751175230994</v>
@@ -10346,13 +10346,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>849.247869574134</v>
+        <v>305.5692851774251</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600407231</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10586,10 +10586,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>403.029938281552</v>
+        <v>849.2478695741536</v>
       </c>
       <c r="P35" t="n">
-        <v>779.2870600407426</v>
+        <v>333.06912874831</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10814,7 +10814,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>11.16868152541317</v>
+        <v>731.1613784661987</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10823,7 +10823,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>849.2478695741672</v>
+        <v>129.2551726335861</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11045,13 +11045,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>45.24036997818725</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11060,13 +11060,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>128.2128919081</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>779.2870600407927</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>779</v>
+        <v>68.8196688228299</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>797.3203508302889</v>
+        <v>849.24786957425</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.287060040839</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -23226,22 +23226,22 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>57.40845813745597</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23271,7 +23271,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -23280,10 +23280,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>328.3285120659748</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -23423,10 +23423,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370704</v>
       </c>
       <c r="R13" t="n">
         <v>501.6021279811511</v>
@@ -23663,13 +23663,13 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>108.2004986247733</v>
+        <v>191.5739783276288</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23885,28 +23885,28 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L19" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>275.8376408970016</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>336.1216064854079</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24134,16 +24134,16 @@
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>191.5739783276288</v>
+        <v>69.04626797189968</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24368,16 +24368,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>361.445564079015</v>
+        <v>22.80679627819029</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>69.04626797189968</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24408,16 +24408,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>68.31450180093421</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -24426,7 +24426,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24465,10 +24465,10 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>89.06488672744541</v>
       </c>
     </row>
     <row r="27">
@@ -24602,7 +24602,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>346.1850752716849</v>
+        <v>5.408275783157308</v>
       </c>
       <c r="O28" t="n">
         <v>415.445564079015</v>
@@ -24614,7 +24614,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24654,7 +24654,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>10.25860861458548</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -24711,7 +24711,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>10.25860861458563</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -24830,10 +24830,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5207738011430365</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>135.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>232.6316114025499</v>
@@ -24848,7 +24848,7 @@
         <v>399.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>56.85733851270868</v>
+        <v>192.925740471631</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -24888,7 +24888,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>10.2586086145855</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -24897,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>10.25860861458553</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -25067,31 +25067,31 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.5207738011430365</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>232.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>283.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>110.3731171152763</v>
+        <v>352.445564079015</v>
       </c>
       <c r="P34" t="n">
         <v>399.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>437.839266425598</v>
+        <v>192.4049666704879</v>
       </c>
       <c r="R34" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>74.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25122,7 +25122,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>10.25860861458554</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>10.25860861433613</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25359,7 +25359,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>10.25860861458554</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -25416,7 +25416,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>10.25860861428237</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -25553,19 +25553,19 @@
         <v>283.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>352.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>295.7751922359946</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>74.37347970285543</v>
+        <v>56.85733851270872</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25599,19 +25599,19 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>220.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>214.3632896068686</v>
+        <v>136.2903678376507</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>214.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>213.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>218.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,10 +25641,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>60.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>304.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25653,16 +25653,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>439.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>448.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>402.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>12.39184176377893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>357.2737972923793</v>
+        <v>222.7928152111537</v>
       </c>
       <c r="S42" t="n">
         <v>276.5639999646113</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>150.4264641910521</v>
+        <v>242.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25769,7 +25769,7 @@
         <v>55.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>38.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25814,7 +25814,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>36.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>57.44364543010755</v>
@@ -25836,7 +25836,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>337.3391557398498</v>
+        <v>170.6714614410739</v>
       </c>
       <c r="E44" t="n">
         <v>331.3632896068686</v>
@@ -25878,10 +25878,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>177.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>212.3047310397533</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -25890,7 +25890,7 @@
         <v>576.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>556.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>565.3734759809475</v>
@@ -25912,10 +25912,10 @@
         <v>311.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>288.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>6.470929359331819</v>
+        <v>274.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>269.6720972219126</v>
@@ -25975,10 +25975,10 @@
         <v>359.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>346.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>326.3913927661343</v>
+        <v>116.6874622276316</v>
       </c>
     </row>
     <row r="46">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11400121.48239069</v>
+        <v>11400121.48239071</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12348338.00755593</v>
+        <v>12348338.00755597</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13137050.25258094</v>
+        <v>13137050.25258097</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13672142.5808387</v>
+        <v>13672142.58083873</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1227892.614324281</v>
+        <v>1227892.61432428</v>
       </c>
       <c r="C2" t="n">
         <v>1227892.61432428</v>
@@ -26299,19 +26299,19 @@
         <v>1192917.563917558</v>
       </c>
       <c r="L2" t="n">
-        <v>1192917.563917558</v>
+        <v>1192917.563917559</v>
       </c>
       <c r="M2" t="n">
-        <v>1192917.563917558</v>
+        <v>1192917.563917577</v>
       </c>
       <c r="N2" t="n">
-        <v>1192917.563917558</v>
+        <v>1192917.563917582</v>
       </c>
       <c r="O2" t="n">
         <v>992272.7745722493</v>
       </c>
       <c r="P2" t="n">
-        <v>673180.6710339505</v>
+        <v>673180.6710339503</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556518.3877202002</v>
+        <v>551678.2037907121</v>
       </c>
       <c r="C4" t="n">
-        <v>554765.5452197595</v>
+        <v>549925.3612902712</v>
       </c>
       <c r="D4" t="n">
-        <v>553010.3248790619</v>
+        <v>548170.1409495736</v>
       </c>
       <c r="E4" t="n">
-        <v>474768.9161162032</v>
+        <v>469977.895301786</v>
       </c>
       <c r="F4" t="n">
-        <v>525348.7383112748</v>
+        <v>520557.7174968576</v>
       </c>
       <c r="G4" t="n">
-        <v>523678.7566207297</v>
+        <v>518887.7358063125</v>
       </c>
       <c r="H4" t="n">
-        <v>522006.457090894</v>
+        <v>517215.4362764768</v>
       </c>
       <c r="I4" t="n">
-        <v>520331.8230037717</v>
+        <v>515540.8021893546</v>
       </c>
       <c r="J4" t="n">
-        <v>464813.3679854201</v>
+        <v>460130.3405348168</v>
       </c>
       <c r="K4" t="n">
-        <v>522819.4679272755</v>
+        <v>518135.704599993</v>
       </c>
       <c r="L4" t="n">
-        <v>521101.9613805412</v>
+        <v>516418.1980532587</v>
       </c>
       <c r="M4" t="n">
-        <v>519382.0000515244</v>
+        <v>514698.236724257</v>
       </c>
       <c r="N4" t="n">
-        <v>517659.5657041207</v>
+        <v>512975.8023768564</v>
       </c>
       <c r="O4" t="n">
-        <v>404347.5537654388</v>
+        <v>399664.5263148356</v>
       </c>
       <c r="P4" t="n">
-        <v>225787.884972441</v>
+        <v>221104.8575218378</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>301314.6266040803</v>
+        <v>306154.8105335683</v>
       </c>
       <c r="C6" t="n">
-        <v>589947.4691045206</v>
+        <v>594787.6530340092</v>
       </c>
       <c r="D6" t="n">
-        <v>591702.6894452184</v>
+        <v>596542.8733747063</v>
       </c>
       <c r="E6" t="n">
-        <v>374943.0451003396</v>
+        <v>379734.065914757</v>
       </c>
       <c r="F6" t="n">
-        <v>547154.5229889413</v>
+        <v>551945.5438033585</v>
       </c>
       <c r="G6" t="n">
-        <v>592024.5046794863</v>
+        <v>596815.5254939038</v>
       </c>
       <c r="H6" t="n">
-        <v>593696.8042093219</v>
+        <v>598487.8250237392</v>
       </c>
       <c r="I6" t="n">
-        <v>595371.4382964441</v>
+        <v>600162.4591108618</v>
       </c>
       <c r="J6" t="n">
-        <v>145236.5932631229</v>
+        <v>149919.6207137259</v>
       </c>
       <c r="K6" t="n">
-        <v>504923.023990283</v>
+        <v>509606.7873175652</v>
       </c>
       <c r="L6" t="n">
-        <v>600240.5305370172</v>
+        <v>604924.2938642999</v>
       </c>
       <c r="M6" t="n">
-        <v>601960.4918660338</v>
+        <v>606644.2551933202</v>
       </c>
       <c r="N6" t="n">
-        <v>603682.9262134376</v>
+        <v>608366.6895407254</v>
       </c>
       <c r="O6" t="n">
-        <v>466188.9108068104</v>
+        <v>470871.9382574137</v>
       </c>
       <c r="P6" t="n">
-        <v>393892.5490615095</v>
+        <v>398575.5765121125</v>
       </c>
     </row>
   </sheetData>
@@ -26975,7 +26975,7 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
         <v>-0</v>
@@ -27005,10 +27005,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>73</v>
@@ -27454,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,10 +27484,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>153.4284074428799</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>303.5095671255643</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27502,7 +27502,7 @@
         <v>400</v>
       </c>
       <c r="Y2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27518,7 +27518,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27575,13 +27575,13 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>114.7450334731913</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>63.2913276047596</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>350.2307325978599</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
@@ -27603,7 +27603,7 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
@@ -27612,13 +27612,13 @@
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>389.1087556380094</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27651,16 +27651,16 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W4" t="n">
         <v>400</v>
-      </c>
-      <c r="W4" t="n">
-        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27679,19 +27679,19 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>400</v>
       </c>
-      <c r="F5" t="n">
-        <v>302.5498086145861</v>
-      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>52.6309682972707</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27755,13 +27755,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
@@ -27797,7 +27797,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>229.8483048521568</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27809,10 +27809,10 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>342.2743756165773</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27837,19 +27837,19 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>373.8591682926689</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
-        <v>311.3347112042522</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
@@ -27882,16 +27882,16 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27922,13 +27922,13 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>400</v>
+        <v>52.63096829726959</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,13 +27958,13 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>302.549808614586</v>
+        <v>400</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27992,10 +27992,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>232.8841597361925</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28037,7 +28037,7 @@
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>342.2743756165773</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28074,7 +28074,7 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
@@ -28083,10 +28083,10 @@
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>262.5015002759334</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28125,16 +28125,16 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>325.6395755681846</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28247,10 +28247,10 @@
         <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>19.11687125883931</v>
+        <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>19.1168712588393</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28399,10 +28399,10 @@
         <v>279</v>
       </c>
       <c r="H14" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="I14" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28484,28 +28484,28 @@
         <v>279</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>155.670590267103</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>279</v>
-      </c>
-      <c r="N15" t="n">
-        <v>261.5913251766234</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>279</v>
@@ -28718,7 +28718,7 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28727,16 +28727,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>217.5442043757545</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
+        <v>155.6705902671029</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>279</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -28876,7 +28876,7 @@
         <v>279</v>
       </c>
       <c r="I20" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>247.42840744288</v>
       </c>
       <c r="S20" t="n">
         <v>279</v>
@@ -28955,7 +28955,7 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -28964,22 +28964,22 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="M21" t="n">
+        <v>155.6705902671029</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>279</v>
-      </c>
-      <c r="N21" t="n">
-        <v>279</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>217.5442043757548</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29113,7 +29113,7 @@
         <v>279</v>
       </c>
       <c r="I23" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>247.42840744288</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29192,13 +29192,13 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J24" t="n">
         <v>279</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>155.670590267103</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -29207,16 +29207,16 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>279</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>217.5442043757548</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29444,13 +29444,13 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="O27" t="n">
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29666,28 +29666,28 @@
         <v>288</v>
       </c>
       <c r="I30" t="n">
+        <v>278.9295434351469</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>288</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>278.929543435147</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>288</v>
@@ -29903,7 +29903,7 @@
         <v>288</v>
       </c>
       <c r="I33" t="n">
-        <v>278.9295434351469</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29912,19 +29912,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>61.80315754379842</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>288</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>288</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988285484</v>
       </c>
       <c r="S35" t="n">
         <v>288</v>
@@ -30140,7 +30140,7 @@
         <v>288</v>
       </c>
       <c r="I36" t="n">
-        <v>278.9295434351469</v>
+        <v>288</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30152,13 +30152,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>278.929543435147</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988286036</v>
       </c>
       <c r="S38" t="n">
         <v>288</v>
@@ -30377,16 +30377,16 @@
         <v>288</v>
       </c>
       <c r="I39" t="n">
+        <v>278.9295434351469</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>288</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>278.929543435147</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -30623,10 +30623,10 @@
         <v>190</v>
       </c>
       <c r="L42" t="n">
-        <v>35.13927063767259</v>
+        <v>190</v>
       </c>
       <c r="M42" t="n">
-        <v>190</v>
+        <v>78.53719264813066</v>
       </c>
       <c r="N42" t="n">
         <v>190</v>
@@ -30696,7 +30696,7 @@
         <v>190</v>
       </c>
       <c r="J43" t="n">
-        <v>89.31810892587444</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K43" t="n">
         <v>190</v>
@@ -30729,7 +30729,7 @@
         <v>190</v>
       </c>
       <c r="U43" t="n">
-        <v>190</v>
+        <v>167.3794978714907</v>
       </c>
       <c r="V43" t="n">
         <v>190</v>
@@ -30854,13 +30854,13 @@
         <v>73</v>
       </c>
       <c r="J45" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>73</v>
       </c>
       <c r="L45" t="n">
-        <v>73</v>
+        <v>57.16851952684466</v>
       </c>
       <c r="M45" t="n">
         <v>73</v>
@@ -30869,10 +30869,10 @@
         <v>73</v>
       </c>
       <c r="O45" t="n">
-        <v>57.16851952684466</v>
+        <v>73</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="Q45" t="n">
         <v>73</v>
@@ -34746,10 +34746,10 @@
         <v>815</v>
       </c>
       <c r="K2" t="n">
+        <v>783.0093003026433</v>
+      </c>
+      <c r="L2" t="n">
         <v>815</v>
-      </c>
-      <c r="L2" t="n">
-        <v>783.0093003026282</v>
       </c>
       <c r="M2" t="n">
         <v>815</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>77.5054859498152</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
@@ -34889,7 +34889,7 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
@@ -34898,13 +34898,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>212.4753000178911</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34937,16 +34937,16 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34983,10 +34983,10 @@
         <v>815</v>
       </c>
       <c r="K5" t="n">
+        <v>783.0093003026475</v>
+      </c>
+      <c r="L5" t="n">
         <v>815</v>
-      </c>
-      <c r="L5" t="n">
-        <v>783.0093003025918</v>
       </c>
       <c r="M5" t="n">
         <v>815</v>
@@ -34998,7 +34998,7 @@
         <v>815</v>
       </c>
       <c r="P5" t="n">
-        <v>815.0000000000011</v>
+        <v>815</v>
       </c>
       <c r="Q5" t="n">
         <v>815</v>
@@ -35123,19 +35123,19 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>92.87826345571237</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>134.7012555841339</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -35168,16 +35168,16 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
@@ -35220,7 +35220,7 @@
         <v>815</v>
       </c>
       <c r="K8" t="n">
-        <v>783.296360343282</v>
+        <v>783.0093003026046</v>
       </c>
       <c r="L8" t="n">
         <v>815</v>
@@ -35235,7 +35235,7 @@
         <v>815</v>
       </c>
       <c r="P8" t="n">
-        <v>814.7129399593185</v>
+        <v>815</v>
       </c>
       <c r="Q8" t="n">
         <v>815</v>
@@ -35360,7 +35360,7 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
@@ -35369,10 +35369,10 @@
         <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>85.86804465581515</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35411,16 +35411,16 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>38.17422271872228</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,25 +35454,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>116.7428182785515</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>619.4144644189528</v>
+        <v>242.7706698795373</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35533,10 +35533,10 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>144.325477496515</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>416.1038546407913</v>
+        <v>210.2207258996306</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>815</v>
+        <v>814.9999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,7 +35706,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>164.5104768795733</v>
+        <v>559.77220722064</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35770,19 +35770,19 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>280.8791965047787</v>
       </c>
       <c r="K15" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M15" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N15" t="n">
-        <v>396.2178752852782</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
         <v>241.4570219027464</v>
@@ -35791,7 +35791,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35934,7 +35934,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>116.7428182785516</v>
+        <v>814.9999999999999</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,10 +35943,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>116.7428182785516</v>
       </c>
       <c r="P17" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36004,7 +36004,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
         <v>125.2086062376757</v>
@@ -36013,16 +36013,16 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>491.6355797244415</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>365.9500421645043</v>
+        <v>242.6206324316071</v>
       </c>
       <c r="N18" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P18" t="n">
         <v>113.6660045146532</v>
@@ -36171,7 +36171,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,13 +36180,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>536.4810879374849</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>164.5104768795733</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36241,7 +36241,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
         <v>125.2086062376757</v>
@@ -36250,13 +36250,13 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M21" t="n">
-        <v>365.9500421645043</v>
+        <v>242.6206324316071</v>
       </c>
       <c r="N21" t="n">
-        <v>413.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
         <v>241.4570219027464</v>
@@ -36265,7 +36265,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>44.46493928527515</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L23" t="n">
-        <v>814.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>237.4900058455002</v>
       </c>
       <c r="N23" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>116.7428182785516</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36478,13 +36478,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
         <v>404.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>191.1038546407913</v>
+        <v>346.7744449078943</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
@@ -36493,7 +36493,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>413.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
         <v>241.4570219027464</v>
@@ -36502,7 +36502,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>44.46493928527515</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36642,10 +36642,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>393.9356333920305</v>
+        <v>774.8401398571939</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36657,10 +36657,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>779.0000000000243</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36730,13 +36730,13 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>153.743421367494</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36879,10 +36879,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230996</v>
+        <v>764.7137390467662</v>
       </c>
       <c r="L29" t="n">
-        <v>442.7455727081297</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,7 +36891,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>394.90695118442</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -36952,13 +36952,13 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>70.87361410865147</v>
+        <v>61.80315754379838</v>
       </c>
       <c r="J30" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>470.0333980759383</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L30" t="n">
         <v>274.091375348687</v>
@@ -36973,7 +36973,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>113.6660045146532</v>
+        <v>401.6660045146532</v>
       </c>
       <c r="Q30" t="n">
         <v>114.9207349095204</v>
@@ -37113,10 +37113,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>11.1686815254459</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>764.7137390468299</v>
+        <v>764.7137390468558</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37125,13 +37125,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
+        <v>235.3214156033326</v>
+      </c>
+      <c r="P32" t="n">
         <v>779.0000000000416</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>61.80315754379833</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37198,7 +37198,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>562.0913753486871</v>
+        <v>335.8945328924854</v>
       </c>
       <c r="M33" t="n">
         <v>86.95004216450428</v>
@@ -37210,7 +37210,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>113.6660045146532</v>
+        <v>401.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>114.9207349095204</v>
@@ -37353,7 +37353,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>47.83862152373115</v>
+        <v>47.83862153205439</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -37365,16 +37365,16 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O35" t="n">
-        <v>332.7820687074596</v>
+        <v>779.0000000000612</v>
       </c>
       <c r="P35" t="n">
-        <v>779.0000000000612</v>
+        <v>332.7820687076286</v>
       </c>
       <c r="Q35" t="n">
         <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.540154394345602e-10</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>61.80315754379838</v>
+        <v>70.87361410865147</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
@@ -37438,13 +37438,13 @@
         <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
-        <v>374.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N36" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>241.4570219027464</v>
+        <v>520.3865653378933</v>
       </c>
       <c r="P36" t="n">
         <v>113.6660045146532</v>
@@ -37593,7 +37593,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>59.00730304915965</v>
+        <v>778.9999999999998</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
@@ -37602,7 +37602,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O38" t="n">
-        <v>779.0000000000748</v>
+        <v>59.00730305949364</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37611,7 +37611,7 @@
         <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.091363304511014e-10</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37663,16 +37663,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>70.87361410865147</v>
+        <v>61.80315754379833</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
-        <v>470.0333980759383</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
-        <v>274.091375348687</v>
+        <v>562.0913753486871</v>
       </c>
       <c r="M39" t="n">
         <v>86.95004216450428</v>
@@ -37824,13 +37824,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>10.19736373309691</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37839,13 +37839,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>57.96502233400758</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>779.0000000001112</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,10 +37909,10 @@
         <v>381.1038546407913</v>
       </c>
       <c r="L42" t="n">
-        <v>309.2306459863596</v>
+        <v>464.091375348687</v>
       </c>
       <c r="M42" t="n">
-        <v>276.9500421645043</v>
+        <v>165.4872348126349</v>
       </c>
       <c r="N42" t="n">
         <v>324.6265501086548</v>
@@ -37982,7 +37982,7 @@
         <v>13.36654437988173</v>
       </c>
       <c r="J43" t="n">
-        <v>54.04916008996668</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>39.04160872554206</v>
+        <v>16.42110659703279</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>779</v>
+        <v>68.8196688228299</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>727.0724812561965</v>
+        <v>779.0000000001576</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>779.0000000001576</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38140,13 +38140,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>198.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K45" t="n">
         <v>264.1038546407913</v>
       </c>
       <c r="L45" t="n">
-        <v>347.091375348687</v>
+        <v>331.2598948755316</v>
       </c>
       <c r="M45" t="n">
         <v>159.9500421645043</v>
@@ -38155,10 +38155,10 @@
         <v>207.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>298.6255414295911</v>
+        <v>314.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>113.6660045146532</v>
+        <v>186.6660045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
